--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbCalendarInfo002.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbCalendarInfo002.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -37,6 +37,10 @@
   </si>
   <si>
     <t>数据状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>错误信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -389,22 +393,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.26953125" customWidth="1"/>
     <col min="2" max="2" width="23.453125" customWidth="1"/>
     <col min="3" max="3" width="18.26953125" customWidth="1"/>
-    <col min="4" max="4" width="18.08984375" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="16.36328125" customWidth="1"/>
-    <col min="8" max="8" width="32" customWidth="1"/>
-    <col min="9" max="9" width="27.08984375" customWidth="1"/>
-    <col min="10" max="10" width="14.08984375" customWidth="1"/>
+    <col min="4" max="5" width="18.08984375" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="16.36328125" customWidth="1"/>
+    <col min="9" max="9" width="32" customWidth="1"/>
+    <col min="10" max="10" width="27.08984375" customWidth="1"/>
+    <col min="11" max="11" width="14.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -418,22 +422,17 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576">
-      <formula1>"01 中国法定节假日,02 美国法定节假日,03 银行间,04 上交所,05 深交所,06 商业银行柜台市场,07 其他,08 香港节假日,09 澳大利亚节假日,10 欧元区节假日,11 美元节假日,12 伦敦节假日"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576">
-      <formula1>"0 否,1是"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbCalendarInfo002.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbCalendarInfo002.xlsx
@@ -36,11 +36,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>数据状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>错误信息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -396,10 +396,11 @@
   <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.26953125" customWidth="1"/>
-    <col min="2" max="2" width="23.453125" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" customWidth="1"/>
-    <col min="4" max="5" width="18.08984375" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="18.26953125" customWidth="1"/>
+    <col min="3" max="3" width="23.453125" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" customWidth="1"/>
+    <col min="5" max="5" width="18.08984375" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="16.36328125" customWidth="1"/>
@@ -410,19 +411,19 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
